--- a/jogos_2024-09-05.xlsx
+++ b/jogos_2024-09-05.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD2" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['21', '85']</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45540.54166666666</v>
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N3" t="n">
         <v>3</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.3</v>
-      </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AB3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['7', '15', '22']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AG3" t="n">
         <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45540.54166666666</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD4" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['21', '85']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45540.54166666666</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['7', '15', '22']</t>
         </is>
       </c>
       <c r="AG5" t="n">
         <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45540.54166666666</v>
